--- a/Checklist - Artefato 4.xlsx
+++ b/Checklist - Artefato 4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/ferrarini_isabela_pucpr_edu_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E03E957-67BF-4F8F-91A1-DA00C1A84FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{102C3030-C2CE-42C9-931C-3C160B8F622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>N°</t>
   </si>
@@ -104,13 +104,46 @@
   </si>
   <si>
     <t>Cada PBI mapeado resolve claramente uma das expectativas ou dores listadas?</t>
+  </si>
+  <si>
+    <t>Faixas de Aderência</t>
+  </si>
+  <si>
+    <t>0-60%</t>
+  </si>
+  <si>
+    <t>Não aderente</t>
+  </si>
+  <si>
+    <t>61-90%</t>
+  </si>
+  <si>
+    <t>Parcialmente aderente</t>
+  </si>
+  <si>
+    <t>91-100%</t>
+  </si>
+  <si>
+    <t>Aderente</t>
+  </si>
+  <si>
+    <t>Auditor de QA:</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>Data:</t>
+  </si>
+  <si>
+    <t>Tempo total:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -122,29 +155,51 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6124E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -167,11 +222,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,6 +288,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,11 +561,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="100.44140625" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="110.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="15.109375" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
@@ -780,10 +895,273 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
+    <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aed73f09-bf5d-4147-a3d9-eca4840d3416" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EED5F-8754-4D16-831A-C7CA03D1BFFF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE3AD36-DAF9-4B5C-8B4B-D3EE63158375}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C52647-21D9-4C34-966B-5FCC3F373667}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Checklist - Artefato 4.xlsx
+++ b/Checklist - Artefato 4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/ferrarini_isabela_pucpr_edu_br/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{102C3030-C2CE-42C9-931C-3C160B8F622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A53D9E-42D4-457C-B023-53FC50E0E9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>N°</t>
   </si>
@@ -137,13 +137,28 @@
   </si>
   <si>
     <t>Tempo total:</t>
+  </si>
+  <si>
+    <t>Aderência Por Área</t>
+  </si>
+  <si>
+    <t>Aderência</t>
+  </si>
+  <si>
+    <t>Total de Perguntas</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não Aplicavél</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -172,20 +187,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +226,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA6124E"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6124E"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,14 +324,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -333,6 +385,11 @@
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FFA6124E"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -571,7 +628,7 @@
     <col min="6" max="6" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +672,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -629,7 +686,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -643,7 +700,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -657,7 +714,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -671,7 +728,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -685,7 +742,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -699,7 +756,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -713,7 +770,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -727,7 +784,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -741,7 +798,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -755,7 +812,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -769,7 +826,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -783,7 +840,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -797,7 +854,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -811,7 +868,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -825,7 +882,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -839,7 +896,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -853,7 +910,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -867,7 +924,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -881,7 +938,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -896,68 +953,118 @@
       <c r="H21" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="6"/>
+      <c r="C23" s="8"/>
+      <c r="E23" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="E24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>32</v>
       </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="14"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>34</v>
       </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="8"/>
+      <c r="C30" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1107,7 +1214,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1116,15 +1223,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C52647-21D9-4C34-966B-5FCC3F373667}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EED5F-8754-4D16-831A-C7CA03D1BFFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1142,26 +1257,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE3AD36-DAF9-4B5C-8B4B-D3EE63158375}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C52647-21D9-4C34-966B-5FCC3F373667}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Checklist - Artefato 4.xlsx
+++ b/Checklist - Artefato 4.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A53D9E-42D4-457C-B023-53FC50E0E9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E982201A-B355-4FB2-A83B-7775601029B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
   <si>
     <t>N°</t>
   </si>
@@ -70,12 +83,6 @@
     <t>Para todas as ações das personas, foram definidos os objetivos que o usuário deve alcançar por meio dessas ações?</t>
   </si>
   <si>
-    <t>Todas as personas do projeto representam perfis diferentes usuários?</t>
-  </si>
-  <si>
-    <t>Foram definidas pelo menos uma feature para cada persona?</t>
-  </si>
-  <si>
     <t>Todas as features possuem relação direta com alguma ação que a persona poderá realizar?</t>
   </si>
   <si>
@@ -130,9 +137,6 @@
     <t>Auditor de QA:</t>
   </si>
   <si>
-    <t>Mariana</t>
-  </si>
-  <si>
     <t>Data:</t>
   </si>
   <si>
@@ -152,13 +156,130 @@
   </si>
   <si>
     <t>Não Aplicavél</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Valores Inválidos</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>Matheus</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Sim. O projeto possui um nome que foi descrito no campo determinado para essa finalidade.</t>
+  </si>
+  <si>
+    <t>Sim. Foram apresentados os problemas pé-existentes que o software busca solicionar.</t>
+  </si>
+  <si>
+    <t>Sim. Foram apresentadas as expextativas para esse sfotware em questão.</t>
+  </si>
+  <si>
+    <t>Não Conforme</t>
+  </si>
+  <si>
+    <t>Classificação de NCs</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>5 dias</t>
+  </si>
+  <si>
+    <t>3 dias</t>
+  </si>
+  <si>
+    <t>1 dia</t>
+  </si>
+  <si>
+    <t>Adicionar no campo "Problems" problemas relacionados diretamente com todas as expectativas definidas para o software. Expectativas que estão faltando um problema diretamente relacionado são: Profissioal com mais visibilidade e maior concentração de serviços especializados.</t>
+  </si>
+  <si>
+    <t>Em andamento</t>
+  </si>
+  <si>
+    <t>Não conforme</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Adicionar "caixas" de dificuldades do usuário no campo de "Personas" que estejam diretamente relacionados a persona de profissional da saúde. Não faz mal repetir problemas caixas de problemas em personas diferentes, afinal um problema de uma persona também pode ser o problema da outra persona.</t>
+  </si>
+  <si>
+    <t>Sim. Ao todo foram definidos 3 perfis diferentes de personas para esse software.</t>
+  </si>
+  <si>
+    <t>Não. No campo definido para apresentar os problemas do software, ficaram faltando alguns problemas relacionados as expectativas, como um relacionado diretamente com a expectativa de "Profissional com mais visibilidade". Apesar de ser apresentado algo relacionado no campo  "Features" na feature do profissional de saúde, algumas expectativas não possuem nada relacionado diretamente a elas no campo "Problems". Também há mais uma expectativa com nada no campo "Problems" relacionado diretamente a ela, a expectiva de "maior concentração de serviços especializados".</t>
+  </si>
+  <si>
+    <t>Não. Não foi encontrado nenhum problema no campo "Problems" relacionado diretamente a persona "Prof. Da Saúde". Apesar de terem sido encontrados problemas que podem sim afetar também o profissional de saúde como a complexidade do app, já que um app complexo não afeta apenas o usuário idoso. Temos também a falta de informação do paciente, onde se um médico não possui as informações básicas de seu paciente o atendimento se torna inviável. Apesar desse problemas fizerem sentido com o perfil de profissional de saúde, nenhum desses ponto está descrito como uma dificuldade direta da persona "Prof. da saúde" no campo de personas.</t>
+  </si>
+  <si>
+    <t>Sim. No campo persona foram definidas as ações que cada persona deverá realizar, como avaliar atendimento na persona  "Idoso".</t>
+  </si>
+  <si>
+    <t>Sim. Ao lado esquedo das personas no campo "Personas" todas as ações estão com seus verbos no infinitivo.</t>
+  </si>
+  <si>
+    <t>Sim. Ao lado direito das personas no campo "Personas", todas as ações possuem um objetivo correspondente.</t>
+  </si>
+  <si>
+    <t>Todas as personas do projeto representam perfis de diferentes usuários?</t>
+  </si>
+  <si>
+    <t>Sim. Todas as personas representam perfis de diferentes usuários.</t>
+  </si>
+  <si>
+    <t>Foi definida pelo menos uma feature para cada persona?</t>
+  </si>
+  <si>
+    <t>Sim. Foi definida exatamente uma feature para cada persona do software.</t>
+  </si>
+  <si>
+    <t>Sim. Cada feature é exatamente uma das ações que a persona poderá realizar.</t>
+  </si>
+  <si>
+    <t>Sim. Cada feature possui ao seu lado esquerdo a dificuldade/estado do sistema antes da implementação da feature.</t>
+  </si>
+  <si>
+    <t>Sim. Cada feature possui ao seu lado direito o estado/objetivo que é desejado que o sistema alcance.</t>
+  </si>
+  <si>
+    <t>Sim. Cada feature possui uma lista de PBIs localizados no campo "PBIs" que correspondem a feature.</t>
+  </si>
+  <si>
+    <t>Sim. Todos os PBIs estão com seus verbos no infinitivo.</t>
+  </si>
+  <si>
+    <t>01 hora e 30 minutos.</t>
+  </si>
+  <si>
+    <t>Os PBIs não estão ordenados de acordo com a jornada cronológica do sistema. Isso faz com que algumas etapas fiquem sem sentido, por exemplo, a funcionalidade "Realizar login na conta" aparece somente depois de "Realizar a busca de profissionais"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reordenar os PBIs de acordo com a jornada cronológica do usuário e segundo as depêndencias de cada PBI, garantindo que etapas essenciais como "Realizar cadastro da Conta" e "Realizar login na conta" precedam funcionalidades outras funcionalidades. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -193,13 +314,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
@@ -214,8 +328,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,8 +364,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -310,49 +464,287 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -378,11 +770,11 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Página1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -402,16 +794,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:H21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B2:I22">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N°"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descrição"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Resultado"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Responsável"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Observações"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Classificação da NCF"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ação Corretiva Indicada"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Situação da NC"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N°" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descrição" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Resultado" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Responsável" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Observações" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Classificação da NCF" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ação Corretiva Indicada" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Situação da NC" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Página1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -618,436 +1010,700 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="B2:AA32"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="110.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="110.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+    </row>
+    <row r="3" spans="2:27" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B4" s="17">
+        <v>2</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B5" s="17">
+        <v>3</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" ht="66" x14ac:dyDescent="0.25">
+      <c r="B6" s="17">
+        <v>4</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B7" s="17">
+        <v>5</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="66" x14ac:dyDescent="0.25">
+      <c r="B8" s="17">
+        <v>6</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="B9" s="17">
+        <v>7</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="B10" s="17">
+        <v>8</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="B11" s="17">
+        <v>9</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B12" s="17">
+        <v>10</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" ht="66" x14ac:dyDescent="0.25">
+      <c r="B13" s="17">
+        <v>11</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" ht="66" x14ac:dyDescent="0.25">
+      <c r="B14" s="17">
+        <v>12</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="B15" s="17">
+        <v>13</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="B16" s="17">
+        <v>14</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="B17" s="17">
+        <v>15</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B18" s="17">
+        <v>16</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="224.4" x14ac:dyDescent="0.25">
+      <c r="B19" s="17">
+        <v>17</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B20" s="17">
+        <v>18</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B21" s="17">
+        <v>19</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B22" s="17">
+        <v>20</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="C24" s="5"/>
+      <c r="F24" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+    </row>
+    <row r="25" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B25" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="7" t="s">
+      <c r="C25" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="E23" s="10" t="s">
+      <c r="F25" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="5" t="s">
+      <c r="H25" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C26" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
+    </row>
+    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="24">
+        <v>0</v>
+      </c>
+      <c r="G27" s="24">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24">
+        <v>0</v>
+      </c>
+      <c r="I27" s="25" t="str">
+        <f>IF(F27-H27 &lt;= 0, "Valores Inválidos", G27/(F27-H27))</f>
+        <v>Valores Inválidos</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="15"/>
+    </row>
+    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="F29" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="34"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="9">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="5" t="s">
+      <c r="C30" s="7">
+        <v>46270</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="6"/>
+      <c r="C31" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
+  <mergeCells count="9">
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
   </mergeCells>
+  <conditionalFormatting sqref="I27">
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>$I$27 = "Valores Inválidos"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>$I$27&lt;=0.6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>AND($I$27 &gt; 0.6, $I$27&lt;=0.9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>$I$27 &gt;0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <tableParts count="1">
@@ -1057,14 +1713,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1214,6 +1862,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1224,22 +1880,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C52647-21D9-4C34-966B-5FCC3F373667}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81EED5F-8754-4D16-831A-C7CA03D1BFFF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1257,6 +1897,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C52647-21D9-4C34-966B-5FCC3F373667}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE3AD36-DAF9-4B5C-8B4B-D3EE63158375}">
   <ds:schemaRefs>
